--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -1,21 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cuong\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E75F2C6-4D93-4E19-AF2D-9F17425BE62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30002"/>
+  <workbookPr/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FA26727-6A84-4710-BD56-6C59CA0E6848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{49A23A8D-3308-41CA-92E7-37734359631B}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,49 +31,74 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>Tên khách</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số giấy tờ </t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
+  <si>
+    <t>Tên người đăng ký</t>
+  </si>
+  <si>
+    <t>Số giấy tờ</t>
   </si>
   <si>
     <t>Loại giấy tờ</t>
   </si>
   <si>
-    <t>Khu vực</t>
-  </si>
-  <si>
-    <t>Biển số xe</t>
+    <t>Biển số</t>
+  </si>
+  <si>
+    <t>Loại phương tiện</t>
   </si>
   <si>
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>Phạm Văn A</t>
+    <t>Phạm Mạnh Cường</t>
   </si>
   <si>
     <t>CMND</t>
   </si>
   <si>
-    <t>20C-00968</t>
+    <t> 20C-00737</t>
+  </si>
+  <si>
+    <t>Xe ô tô dưới 29 chỗ, xe tải dưới 5 tấn</t>
+  </si>
+  <si>
+    <t>Phạm Mạnh A</t>
+  </si>
+  <si>
+    <t> </t>
+  </si>
+  <si>
+    <t>Phạm Mạnh B</t>
+  </si>
+  <si>
+    <t>Phạm Mạnh C</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="00000"/>
-  </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -89,12 +109,40 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -107,25 +155,281 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -135,6 +439,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F4B96147-F8E0-407C-8D05-9C428644A56D}" name="Table1" displayName="Table1" ref="A1:D5" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5" tableBorderDxfId="4">
+  <autoFilter ref="A1:D5" xr:uid="{F4B96147-F8E0-407C-8D05-9C428644A56D}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{D75BBB77-51BE-4D12-805B-0FB902DD3B15}" name="Tên người đăng ký" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{A74A3E16-D2FA-4FA3-8593-A5A8DC52477C}" name="Số giấy tờ" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{1A544B2B-7C74-4DF4-A25A-4B0EABF15A18}" name="Loại giấy tờ" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{3B74CC6E-5E10-473A-BC50-F4896F5C71D3}" name="Biển số" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -154,13 +471,13 @@
         <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="145F82"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="E87331"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="186C24"/>
       </a:accent3>
       <a:accent4>
         <a:srgbClr val="0F9ED5"/>
@@ -180,7 +497,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -446,60 +763,120 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D7C23A9-07B5-4A5E-AEAF-C43FE9E711E2}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>370996688114</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1"/>
+      <c r="E2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1">
+        <v>370996688114</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1">
+        <v>370996688114</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="7">
+        <v>370996688114</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30002"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FA26727-6A84-4710-BD56-6C59CA0E6848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{978B3CD7-507E-4371-976D-A59C5A848C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,9 +31,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
   <si>
     <t>Tên người đăng ký</t>
+  </si>
+  <si>
+    <t>Số điện thoại</t>
   </si>
   <si>
     <t>Số giấy tờ</t>
@@ -219,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -231,11 +234,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
     <dxf>
       <font>
         <b val="0"/>
@@ -260,6 +264,42 @@
           <color rgb="FF000000"/>
         </left>
         <right/>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
@@ -442,10 +482,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F4B96147-F8E0-407C-8D05-9C428644A56D}" name="Table1" displayName="Table1" ref="A1:D5" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5" tableBorderDxfId="4">
-  <autoFilter ref="A1:D5" xr:uid="{F4B96147-F8E0-407C-8D05-9C428644A56D}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D75BBB77-51BE-4D12-805B-0FB902DD3B15}" name="Tên người đăng ký" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F4B96147-F8E0-407C-8D05-9C428644A56D}" name="Table1" displayName="Table1" ref="A1:E5" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" tableBorderDxfId="5">
+  <autoFilter ref="A1:E5" xr:uid="{F4B96147-F8E0-407C-8D05-9C428644A56D}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{D75BBB77-51BE-4D12-805B-0FB902DD3B15}" name="Tên người đăng ký" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{31AE15D9-62AE-43CE-BDD0-88BD336B22C4}" name="Số điện thoại" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{A74A3E16-D2FA-4FA3-8593-A5A8DC52477C}" name="Số giấy tờ" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{1A544B2B-7C74-4DF4-A25A-4B0EABF15A18}" name="Loại giấy tờ" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{3B74CC6E-5E10-473A-BC50-F4896F5C71D3}" name="Biển số" dataDxfId="0"/>
@@ -771,107 +812,114 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
-    <col min="2" max="2" width="29.5703125" customWidth="1"/>
-    <col min="3" max="3" width="35.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.5703125" customWidth="1"/>
+    <col min="4" max="4" width="35.5703125" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="1">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1">
         <v>370996688114</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="9"/>
+      <c r="F2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1">
+        <v>370996688114</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1">
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1">
         <v>370996688114</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="2"/>
+      <c r="D4" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2"/>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:7">
+      <c r="A5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7">
+        <v>370996688114</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1">
-        <v>370996688114</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="7">
-        <v>370996688114</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30117"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{978B3CD7-507E-4371-976D-A59C5A848C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{172C7496-7203-4024-A05C-0F556B85FE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,14 +31,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
   <si>
     <t>Tên người đăng ký</t>
   </si>
   <si>
-    <t>Số điện thoại</t>
-  </si>
-  <si>
     <t>Số giấy tờ</t>
   </si>
   <si>
@@ -48,9 +45,6 @@
     <t>Biển số</t>
   </si>
   <si>
-    <t>Loại phương tiện</t>
-  </si>
-  <si>
     <t>Ghi chú</t>
   </si>
   <si>
@@ -61,9 +55,6 @@
   </si>
   <si>
     <t> 20C-00737</t>
-  </si>
-  <si>
-    <t>Xe ô tô dưới 29 chỗ, xe tải dưới 5 tấn</t>
   </si>
   <si>
     <t>Phạm Mạnh A</t>
@@ -222,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -234,12 +225,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="7">
     <dxf>
       <font>
         <b val="0"/>
@@ -264,42 +254,6 @@
           <color rgb="FF000000"/>
         </left>
         <right/>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
@@ -482,11 +436,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F4B96147-F8E0-407C-8D05-9C428644A56D}" name="Table1" displayName="Table1" ref="A1:E5" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" tableBorderDxfId="5">
-  <autoFilter ref="A1:E5" xr:uid="{F4B96147-F8E0-407C-8D05-9C428644A56D}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D75BBB77-51BE-4D12-805B-0FB902DD3B15}" name="Tên người đăng ký" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{31AE15D9-62AE-43CE-BDD0-88BD336B22C4}" name="Số điện thoại" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F4B96147-F8E0-407C-8D05-9C428644A56D}" name="Table1" displayName="Table1" ref="A1:D5" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5" tableBorderDxfId="4">
+  <autoFilter ref="A1:D5" xr:uid="{F4B96147-F8E0-407C-8D05-9C428644A56D}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{D75BBB77-51BE-4D12-805B-0FB902DD3B15}" name="Tên người đăng ký" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{A74A3E16-D2FA-4FA3-8593-A5A8DC52477C}" name="Số giấy tờ" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{1A544B2B-7C74-4DF4-A25A-4B0EABF15A18}" name="Loại giấy tờ" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{3B74CC6E-5E10-473A-BC50-F4896F5C71D3}" name="Biển số" dataDxfId="0"/>
@@ -812,114 +765,91 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="19.42578125" customWidth="1"/>
-    <col min="3" max="3" width="29.5703125" customWidth="1"/>
-    <col min="4" max="4" width="35.5703125" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="B2" s="1">
+        <v>370996688114</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="D2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="9"/>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1">
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1">
         <v>370996688114</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="6" t="s">
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="9"/>
+      <c r="B4" s="1">
+        <v>370996688114</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2"/>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1">
+      <c r="B5" s="7">
         <v>370996688114</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1">
-        <v>370996688114</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7">
-        <v>370996688114</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="2"/>
+      <c r="C5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30117"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30203"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{172C7496-7203-4024-A05C-0F556B85FE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3244B1F0-6B05-470E-9FAF-7623466FD1DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
   <si>
     <t>Tên người đăng ký</t>
   </si>
@@ -45,6 +45,9 @@
     <t>Biển số</t>
   </si>
   <si>
+    <t>Khu vực</t>
+  </si>
+  <si>
     <t>Ghi chú</t>
   </si>
   <si>
@@ -57,16 +60,58 @@
     <t> 20C-00737</t>
   </si>
   <si>
+    <t>VP</t>
+  </si>
+  <si>
     <t>Phạm Mạnh A</t>
   </si>
   <si>
     <t> </t>
   </si>
   <si>
+    <t>KN, KX</t>
+  </si>
+  <si>
     <t>Phạm Mạnh B</t>
   </si>
   <si>
+    <t>TC</t>
+  </si>
+  <si>
     <t>Phạm Mạnh C</t>
+  </si>
+  <si>
+    <t>Chú thích:</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tên khu vực </t>
+  </si>
+  <si>
+    <t>Văn phòng</t>
+  </si>
+  <si>
+    <t>KN</t>
+  </si>
+  <si>
+    <t>Kho nhập</t>
+  </si>
+  <si>
+    <t>KX</t>
+  </si>
+  <si>
+    <t>Kho xuất</t>
+  </si>
+  <si>
+    <t>K3</t>
+  </si>
+  <si>
+    <t>Kho 3</t>
+  </si>
+  <si>
+    <t>Tất cả</t>
   </si>
 </sst>
 </file>
@@ -84,15 +129,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="1"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -103,25 +145,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -209,27 +238,54 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
     <dxf>
       <font>
         <b val="0"/>
@@ -243,9 +299,45 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FF000000"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FF000000"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -277,9 +369,7 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <name val="Arial"/>
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -313,9 +403,7 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <name val="Arial"/>
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -349,9 +437,7 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <name val="Arial"/>
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -395,9 +481,7 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <name val="Arial"/>
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -415,9 +499,7 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <name val="Arial"/>
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -436,13 +518,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F4B96147-F8E0-407C-8D05-9C428644A56D}" name="Table1" displayName="Table1" ref="A1:D5" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5" tableBorderDxfId="4">
-  <autoFilter ref="A1:D5" xr:uid="{F4B96147-F8E0-407C-8D05-9C428644A56D}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D75BBB77-51BE-4D12-805B-0FB902DD3B15}" name="Tên người đăng ký" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{A74A3E16-D2FA-4FA3-8593-A5A8DC52477C}" name="Số giấy tờ" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{1A544B2B-7C74-4DF4-A25A-4B0EABF15A18}" name="Loại giấy tờ" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{3B74CC6E-5E10-473A-BC50-F4896F5C71D3}" name="Biển số" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F4B96147-F8E0-407C-8D05-9C428644A56D}" name="Table1" displayName="Table1" ref="A1:E5" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6" tableBorderDxfId="5">
+  <autoFilter ref="A1:E5" xr:uid="{F4B96147-F8E0-407C-8D05-9C428644A56D}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{D75BBB77-51BE-4D12-805B-0FB902DD3B15}" name="Tên người đăng ký" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{A74A3E16-D2FA-4FA3-8593-A5A8DC52477C}" name="Số giấy tờ" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{1A544B2B-7C74-4DF4-A25A-4B0EABF15A18}" name="Loại giấy tờ" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{3B74CC6E-5E10-473A-BC50-F4896F5C71D3}" name="Biển số" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{69BE80EE-123A-4348-B23A-11886C81368E}" name="Khu vực" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -765,91 +848,168 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
-    <col min="2" max="2" width="29.5703125" customWidth="1"/>
-    <col min="3" max="3" width="35.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" style="7" customWidth="1"/>
+    <col min="6" max="9" width="9.140625" style="7"/>
+    <col min="10" max="10" width="9.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="7"/>
+    <col min="12" max="12" width="11.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="6"/>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1">
+    <row r="2" spans="1:12">
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4">
         <v>370996688114</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="9"/>
+      <c r="D2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="6"/>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1">
+    <row r="3" spans="1:12">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4">
         <v>370996688114</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="4">
+        <v>370996688114</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="11">
+        <v>370996688114</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="J6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="K7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="2"/>
+      <c r="L7" s="13" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1">
-        <v>370996688114</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2"/>
+    <row r="8" spans="1:12">
+      <c r="K8" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="7">
-        <v>370996688114</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="2"/>
+    <row r="9" spans="1:12">
+      <c r="K9" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="K10" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="K11" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11" s="13" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
